--- a/data/trans_orig/Viv_Temp_insuf-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Viv_Temp_insuf-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17231</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12310</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21721</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23288</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17818</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29096</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>46566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33306</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28816</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38227</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>34223</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28415</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39693</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>59,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47612</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>76495</t>
+          <t>63962</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84815</t>
+          <t>70758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57591</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78530</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58631</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49224</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>68610</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78493</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67317</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137124</t>
+          <t>121536</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>107429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152660</t>
+          <t>133746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89953</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78992</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>99931</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100668</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90689</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110075</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>63,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>104061</t>
+          <t>91551</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93028</t>
+          <t>81964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115237</t>
+          <t>100741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>204729</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189193</t>
+          <t>169293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220001</t>
+          <t>195610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95855</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80238</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>67906</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91183</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>46,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83141</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>69820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>92041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>163380</t>
+          <t>163679</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145889</t>
+          <t>145869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183459</t>
+          <t>180102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117273</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>103314</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>92915</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81970</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105247</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>82761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>221320</t>
+          <t>210292</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201241</t>
+          <t>193869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238811</t>
+          <t>228102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173153</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173153</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173153</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>174802</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>174802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>174802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>373971</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>373971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>373971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>107039</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>89431</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>122404</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97207</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>67451</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>115429</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>87894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124777</t>
+          <t>116770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>203651</t>
+          <t>209194</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168248</t>
+          <t>187792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229808</t>
+          <t>232478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>185606</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170241</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>203214</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>177251</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159029</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207007</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>199038</t>
+          <t>153323</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180706</t>
+          <t>138708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216014</t>
+          <t>167584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>376290</t>
+          <t>338928</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350133</t>
+          <t>315644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411693</t>
+          <t>360330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>273735</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>297023</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>259364</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>227582</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>284129</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>239667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>314141</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>533073</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>503894</t>
+          <t>499121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>581534</t>
+          <t>564113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>426137</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>402849</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>451501</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>405057</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>380292</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>436839</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>473776</t>
+          <t>368549</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446887</t>
+          <t>347153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497175</t>
+          <t>388220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>878833</t>
+          <t>794686</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>843915</t>
+          <t>763646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>921555</t>
+          <t>828638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
